--- a/travelsheet.xlsx
+++ b/travelsheet.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\@master_repo\workstation\social-post\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABB954D-DDD8-4358-BFDF-05DC6EA5ACBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +24,183 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="55">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Place</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Time Taken</t>
+  </si>
+  <si>
+    <t>Stay</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>Place to Visit</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>kolkata</t>
+  </si>
+  <si>
+    <t>Journey</t>
+  </si>
+  <si>
+    <t>New Delhi</t>
+  </si>
+  <si>
+    <t>13:10PM</t>
+  </si>
+  <si>
+    <t>Kota</t>
+  </si>
+  <si>
+    <t>18:05 PM</t>
+  </si>
+  <si>
+    <t>Hotel</t>
+  </si>
+  <si>
+    <t>lodgeing</t>
+  </si>
+  <si>
+    <t>Check in</t>
+  </si>
+  <si>
+    <t>Hotel Chandan</t>
+  </si>
+  <si>
+    <t>Kota River Side</t>
+  </si>
+  <si>
+    <t>Check out</t>
+  </si>
+  <si>
+    <t>6-8</t>
+  </si>
+  <si>
+    <t>Kota Museum</t>
+  </si>
+  <si>
+    <t>Kota Fort *</t>
+  </si>
+  <si>
+    <t>10-11</t>
+  </si>
+  <si>
+    <t>GaperNath</t>
+  </si>
+  <si>
+    <t>Rawatbhata</t>
+  </si>
+  <si>
+    <t>Group of Barolia Temples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Chuliya Waterfall</t>
+  </si>
+  <si>
+    <t>Padajhar Waterfalls</t>
+  </si>
+  <si>
+    <t>Gandhisagar </t>
+  </si>
+  <si>
+    <t>Gandhisagar Dam</t>
+  </si>
+  <si>
+    <t>Chambal  Sunset Point</t>
+  </si>
+  <si>
+    <t>14-15</t>
+  </si>
+  <si>
+    <t>15-16</t>
+  </si>
+  <si>
+    <t>Chandwasa</t>
+  </si>
+  <si>
+    <t>Shree Dharmrajeshwara Temple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bhanpura </t>
+  </si>
+  <si>
+    <t>Hotel Rudrakhs</t>
+  </si>
+  <si>
+    <t>Maharaja Yashwant Rao Holkar Chhatri, GP8Q+VC2, Madhya Pradesh 458775</t>
+  </si>
+  <si>
+    <t>Bade Mahadev</t>
+  </si>
+  <si>
+    <t>Kakuni</t>
+  </si>
+  <si>
+    <t>Kakuni Temple Complex</t>
+  </si>
+  <si>
+    <t>Jhalwarpatan</t>
+  </si>
+  <si>
+    <t>Jhalwar Hotel</t>
+  </si>
+  <si>
+    <t>Howrah Rajdhani Express</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day </t>
+  </si>
+  <si>
+    <t>Day 1</t>
+  </si>
+  <si>
+    <t>Day 2</t>
+  </si>
+  <si>
+    <t>12218 - Kerala Sampark Kranti Express⁩</t>
+  </si>
+  <si>
+    <t>Not able to visit it close to visitor</t>
+  </si>
+  <si>
+    <t>Rana Pratap Sagar Dam</t>
+  </si>
+  <si>
+    <t>Mini Goa Gandhi Sagar</t>
+  </si>
+  <si>
+    <t>Day 3</t>
+  </si>
+  <si>
+    <t>Day 5</t>
+  </si>
+  <si>
+    <t>Day 4</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="d\-mmm\ \(ddd\)"/>
+  </numFmts>
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +208,341 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -45,15 +550,238 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="16" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="20" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="20" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="20" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="19" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="22" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +1058,555 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K63"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" style="8" customWidth="1"/>
+    <col min="3" max="4" width="8.7265625" style="8"/>
+    <col min="5" max="5" width="10.453125" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="65.7265625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.7265625" style="8"/>
+    <col min="9" max="9" width="28" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.453125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="12"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0.71875</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" s="10">
+        <v>46267</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0.4201388888888889</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="10">
+        <v>46267</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.19097222222222221</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="10">
+        <v>46267</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="9"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" s="10">
+        <v>46267</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="10">
+        <v>46268</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="7">
+        <v>9</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" s="7"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="7">
+        <v>12</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="10">
+        <v>46269</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="7">
+        <v>13</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C16" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C20" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C21" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="10">
+        <v>46270</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C24" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C26" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C27" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C28" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="7"/>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C37" s="7"/>
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C38" s="7"/>
+      <c r="F38" s="7"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C42" s="7"/>
+      <c r="F42" s="7"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C43" s="7"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C44" s="7"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C45" s="7"/>
+      <c r="F45" s="7"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A52" s="10"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="7"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="11"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C54" s="7"/>
+      <c r="F54" s="7"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C55" s="7"/>
+      <c r="F55" s="7"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C57" s="7"/>
+      <c r="F57" s="7"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A59" s="10"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="14"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A60" s="10"/>
+      <c r="B60" s="10"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A61" s="10"/>
+      <c r="B61" s="10"/>
+      <c r="D61" s="5"/>
+      <c r="F61" s="7"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A62" s="10"/>
+      <c r="B62" s="10"/>
+      <c r="D62" s="5"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A63" s="10"/>
+      <c r="B63" s="10"/>
+      <c r="D63" s="5"/>
+      <c r="F63" s="7"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/travelsheet.xlsx
+++ b/travelsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\@master_repo\workstation\social-post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABB954D-DDD8-4358-BFDF-05DC6EA5ACBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F86234-7F75-4499-BD7D-47D763585C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="113">
   <si>
     <t>Date</t>
   </si>
@@ -33,42 +33,21 @@
     <t>Place</t>
   </si>
   <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Time Taken</t>
-  </si>
-  <si>
-    <t>Stay</t>
-  </si>
-  <si>
     <t>Mode</t>
   </si>
   <si>
-    <t>Place to Visit</t>
-  </si>
-  <si>
     <t>Note</t>
   </si>
   <si>
-    <t>kolkata</t>
-  </si>
-  <si>
     <t>Journey</t>
   </si>
   <si>
     <t>New Delhi</t>
   </si>
   <si>
-    <t>13:10PM</t>
-  </si>
-  <si>
     <t>Kota</t>
   </si>
   <si>
-    <t>18:05 PM</t>
-  </si>
-  <si>
     <t>Hotel</t>
   </si>
   <si>
@@ -81,24 +60,9 @@
     <t>Hotel Chandan</t>
   </si>
   <si>
-    <t>Kota River Side</t>
-  </si>
-  <si>
     <t>Check out</t>
   </si>
   <si>
-    <t>6-8</t>
-  </si>
-  <si>
-    <t>Kota Museum</t>
-  </si>
-  <si>
-    <t>Kota Fort *</t>
-  </si>
-  <si>
-    <t>10-11</t>
-  </si>
-  <si>
     <t>GaperNath</t>
   </si>
   <si>
@@ -108,10 +72,6 @@
     <t>Group of Barolia Temples</t>
   </si>
   <si>
-    <t xml:space="preserve">
-Chuliya Waterfall</t>
-  </si>
-  <si>
     <t>Padajhar Waterfalls</t>
   </si>
   <si>
@@ -124,12 +84,6 @@
     <t>Chambal  Sunset Point</t>
   </si>
   <si>
-    <t>14-15</t>
-  </si>
-  <si>
-    <t>15-16</t>
-  </si>
-  <si>
     <t>Chandwasa</t>
   </si>
   <si>
@@ -142,9 +96,6 @@
     <t>Hotel Rudrakhs</t>
   </si>
   <si>
-    <t>Maharaja Yashwant Rao Holkar Chhatri, GP8Q+VC2, Madhya Pradesh 458775</t>
-  </si>
-  <si>
     <t>Bade Mahadev</t>
   </si>
   <si>
@@ -157,9 +108,6 @@
     <t>Jhalwarpatan</t>
   </si>
   <si>
-    <t>Jhalwar Hotel</t>
-  </si>
-  <si>
     <t>Howrah Rajdhani Express</t>
   </si>
   <si>
@@ -172,18 +120,12 @@
     <t>Day 2</t>
   </si>
   <si>
-    <t>12218 - Kerala Sampark Kranti Express⁩</t>
-  </si>
-  <si>
     <t>Not able to visit it close to visitor</t>
   </si>
   <si>
     <t>Rana Pratap Sagar Dam</t>
   </si>
   <si>
-    <t>Mini Goa Gandhi Sagar</t>
-  </si>
-  <si>
     <t>Day 3</t>
   </si>
   <si>
@@ -191,6 +133,237 @@
   </si>
   <si>
     <t>Day 4</t>
+  </si>
+  <si>
+    <t>Jhalwar</t>
+  </si>
+  <si>
+    <t>Government Museum</t>
+  </si>
+  <si>
+    <t>Sukh Mahal</t>
+  </si>
+  <si>
+    <t>Bundi</t>
+  </si>
+  <si>
+    <t>Gagron Fort</t>
+  </si>
+  <si>
+    <t>Chauth Mata Mandir</t>
+  </si>
+  <si>
+    <t>Sherghare Fort</t>
+  </si>
+  <si>
+    <t>Artu</t>
+  </si>
+  <si>
+    <t>Baran</t>
+  </si>
+  <si>
+    <t>84 Pillared Cenotaph</t>
+  </si>
+  <si>
+    <t>Taragarh Fort</t>
+  </si>
+  <si>
+    <t>RockPainting</t>
+  </si>
+  <si>
+    <t>Bhimlat Waterfalls</t>
+  </si>
+  <si>
+    <t>Tribal Village</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Howrah</t>
+  </si>
+  <si>
+    <t>Sun Temple</t>
+  </si>
+  <si>
+    <t>Shantinath Digamber jain Temple</t>
+  </si>
+  <si>
+    <t>Mini Goa, Gandhi Sagar</t>
+  </si>
+  <si>
+    <t>Gagron Fort View Point</t>
+  </si>
+  <si>
+    <t>Gagron</t>
+  </si>
+  <si>
+    <t>Gadiya Mandir </t>
+  </si>
+  <si>
+    <t>Temple Ruin</t>
+  </si>
+  <si>
+    <t>Surya Hotel</t>
+  </si>
+  <si>
+    <t>Shergarh</t>
+  </si>
+  <si>
+    <t>Bansthuni </t>
+  </si>
+  <si>
+    <t>Mini Khajuraho Temple</t>
+  </si>
+  <si>
+    <t>7 Wonder Park</t>
+  </si>
+  <si>
+    <t>12218 - Kerala Sampark Kranti Express</t>
+  </si>
+  <si>
+    <t>Maharaja Yashwant Rao Holkar Chhatri</t>
+  </si>
+  <si>
+    <t>Mewar SF Express</t>
+  </si>
+  <si>
+    <t>Kota Rail Staion</t>
+  </si>
+  <si>
+    <t>Day 6</t>
+  </si>
+  <si>
+    <t>Day 7</t>
+  </si>
+  <si>
+    <t>Day 8</t>
+  </si>
+  <si>
+    <t>Day 9</t>
+  </si>
+  <si>
+    <t>Day 10</t>
+  </si>
+  <si>
+    <t>Day 11</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Boarding</t>
+  </si>
+  <si>
+    <t>Getting-off</t>
+  </si>
+  <si>
+    <t>Sight-Seeing</t>
+  </si>
+  <si>
+    <t>Kanya Dah Temple Ruin</t>
+  </si>
+  <si>
+    <t>Bhimlat</t>
+  </si>
+  <si>
+    <t>Raniji ki Baori</t>
+  </si>
+  <si>
+    <t>Nagar Sagar Kund</t>
+  </si>
+  <si>
+    <t>Nizamuddin Station</t>
+  </si>
+  <si>
+    <t>Genre</t>
+  </si>
+  <si>
+    <t>Traveling</t>
+  </si>
+  <si>
+    <t>Station</t>
+  </si>
+  <si>
+    <t>Museum</t>
+  </si>
+  <si>
+    <t>Fort</t>
+  </si>
+  <si>
+    <t>Dam</t>
+  </si>
+  <si>
+    <t>Waterfall</t>
+  </si>
+  <si>
+    <t>Village</t>
+  </si>
+  <si>
+    <t>Chambal River Front</t>
+  </si>
+  <si>
+    <t>Park</t>
+  </si>
+  <si>
+    <t>Kota Govt Museum</t>
+  </si>
+  <si>
+    <t>Kishor Sagar Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kota Garh Palace </t>
+  </si>
+  <si>
+    <t>Lake</t>
+  </si>
+  <si>
+    <t>Nature</t>
+  </si>
+  <si>
+    <t>Architectural</t>
+  </si>
+  <si>
+    <t>Sawariya Guest House</t>
+  </si>
+  <si>
+    <t>Chuliya Waterfall</t>
+  </si>
+  <si>
+    <t>View Point</t>
+  </si>
+  <si>
+    <t>Vishal Hotel</t>
+  </si>
+  <si>
+    <t>Ramgarh</t>
+  </si>
+  <si>
+    <t>Bhand Devara Temple</t>
+  </si>
+  <si>
+    <t>Ramghar Mata Temple</t>
+  </si>
+  <si>
+    <t>Hindu Temple</t>
+  </si>
+  <si>
+    <t>Ramghar Creater View</t>
+  </si>
+  <si>
+    <t>Ramghar Fort</t>
+  </si>
+  <si>
+    <t>Rock Art</t>
+  </si>
+  <si>
+    <t>Howrah Rail Station</t>
+  </si>
+  <si>
+    <t>Delhi Rail Station</t>
   </si>
 </sst>
 </file>
@@ -200,7 +373,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\-mmm\ \(ddd\)"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,12 +512,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -702,41 +869,22 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="16" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="20" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="20" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="20" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="19" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="22" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1059,553 +1207,1207 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:X75"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.36328125" style="8" customWidth="1"/>
-    <col min="3" max="4" width="8.7265625" style="8"/>
-    <col min="5" max="5" width="10.453125" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="65.7265625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.7265625" style="8"/>
-    <col min="9" max="9" width="28" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.453125" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.7265625" style="8"/>
+    <col min="1" max="1" width="11.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1" s="12" t="s">
+      <c r="B1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="F1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="12"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="10">
+      <c r="I1" s="4"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
         <v>46266</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>46</v>
+      <c r="B2" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="6">
-        <v>0.70138888888888884</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.71875</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>9</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="10">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>46267</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="C18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="C19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="C20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="C21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="C22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="C23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="C25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="C26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="C27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="C28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="C29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+      <c r="W30" s="1"/>
+      <c r="X30" s="1"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+    </row>
+    <row r="35" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C35" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="5"/>
+      <c r="C36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C42" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C43" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C48" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C49" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C50" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C51" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C52" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="5">
-        <v>0.4201388888888889</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="10">
-        <v>46267</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.19097222222222221</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="E52" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C53" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="10">
-        <v>46267</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="9"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" s="10">
-        <v>46267</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9" s="10">
-        <v>46268</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="7">
-        <v>9</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="8" t="s">
+      <c r="E53" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="7">
-        <v>12</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C13" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="8" t="s">
+      <c r="E54" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2"/>
+      <c r="C56" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="2"/>
+      <c r="C57" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="2"/>
+      <c r="C58" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C59" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="10">
-        <v>46269</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="7">
-        <v>13</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C16" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="16" t="s">
+      <c r="D63" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="C65" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C17" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C18" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C20" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C21" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="10">
-        <v>46270</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C24" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C25" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C26" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F26" s="7" t="s">
+      <c r="E65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C27" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C28" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C32" s="7"/>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C33" s="7"/>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C34" s="7"/>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C35" s="7"/>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="7"/>
-      <c r="F36" s="7"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C37" s="7"/>
-      <c r="F37" s="7"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C38" s="7"/>
-      <c r="F38" s="7"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C42" s="7"/>
-      <c r="F42" s="7"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C43" s="7"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C44" s="7"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C45" s="7"/>
-      <c r="F45" s="7"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="10"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="10"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="11"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C54" s="7"/>
-      <c r="F54" s="7"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C55" s="7"/>
-      <c r="F55" s="7"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C57" s="7"/>
-      <c r="F57" s="7"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" s="10"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="14"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60" s="10"/>
-      <c r="B60" s="10"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" s="10"/>
-      <c r="B61" s="10"/>
-      <c r="D61" s="5"/>
-      <c r="F61" s="7"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62" s="10"/>
-      <c r="B62" s="10"/>
-      <c r="D62" s="5"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" s="10"/>
-      <c r="B63" s="10"/>
-      <c r="D63" s="5"/>
-      <c r="F63" s="7"/>
-    </row>
+      <c r="D66" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="68" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="69" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="70" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="71" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="72" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B72" s="2"/>
+    </row>
+    <row r="73" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B73" s="2"/>
+    </row>
+    <row r="74" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="2"/>
+    </row>
+    <row r="75" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/travelsheet.xlsx
+++ b/travelsheet.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\@master_repo\workstation\social-post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F86234-7F75-4499-BD7D-47D763585C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6177A29-CD7C-416A-9AA4-0702A72D8393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="timeline" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/travelsheet.xlsx
+++ b/travelsheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\@master_repo\workstation\social-post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6177A29-CD7C-416A-9AA4-0702A72D8393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58F7A5B-2000-4EF5-9EF2-3893023B812D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/travelsheet.xlsx
+++ b/travelsheet.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\@master_repo\workstation\social-post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58F7A5B-2000-4EF5-9EF2-3893023B812D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E114A655-6EBA-4435-9FCF-2704ACE85D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeline" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="196">
   <si>
     <t>Date</t>
   </si>
@@ -364,6 +365,255 @@
   </si>
   <si>
     <t>Delhi Rail Station</t>
+  </si>
+  <si>
+    <t>Serial</t>
+  </si>
+  <si>
+    <t>Geo-Location</t>
+  </si>
+  <si>
+    <t>02-Sep,(Wed) - Day 2</t>
+  </si>
+  <si>
+    <t>Chambal River Front, Kota</t>
+  </si>
+  <si>
+    <t>25.176400, 75.846700</t>
+  </si>
+  <si>
+    <t>03-Sep,(Thu) - Day 3</t>
+  </si>
+  <si>
+    <t>Kishor Sagar Lake, Kota</t>
+  </si>
+  <si>
+    <t>25.182500, 75.833000</t>
+  </si>
+  <si>
+    <t>Kota Govt Museum, Kota</t>
+  </si>
+  <si>
+    <t>25.182000, 75.833800</t>
+  </si>
+  <si>
+    <t>Kota Garh Palace, Kota</t>
+  </si>
+  <si>
+    <t>25.182700, 75.833000</t>
+  </si>
+  <si>
+    <t>GaperNath, Kota</t>
+  </si>
+  <si>
+    <t>25.086000, 75.925000</t>
+  </si>
+  <si>
+    <t>Group of Barolia Temples, Rawatbhata</t>
+  </si>
+  <si>
+    <t>24.931000, 75.575000</t>
+  </si>
+  <si>
+    <t>Rana Pratap Sagar Dam, Rawatbhata</t>
+  </si>
+  <si>
+    <t>24.927000, 75.586000</t>
+  </si>
+  <si>
+    <t>04-Sep,(Fri) - Day 4</t>
+  </si>
+  <si>
+    <t>Chuliya Waterfall, Gandhisagar</t>
+  </si>
+  <si>
+    <t>24.740000, 75.625000</t>
+  </si>
+  <si>
+    <t>Padajhar Waterfalls, Gandhisagar</t>
+  </si>
+  <si>
+    <t>24.780000, 75.650000</t>
+  </si>
+  <si>
+    <t>Gandhisagar Dam, Gandhisagar</t>
+  </si>
+  <si>
+    <t>24.713000, 75.555000</t>
+  </si>
+  <si>
+    <t>Chambal  Sunset Point, Gandhisagar</t>
+  </si>
+  <si>
+    <t>24.710000, 75.560000</t>
+  </si>
+  <si>
+    <t>Shree Dharmrajeshwara Temple, Chandwasa</t>
+  </si>
+  <si>
+    <t>24.265000, 75.650000</t>
+  </si>
+  <si>
+    <t>05-Sep,(Sat) - Day 5</t>
+  </si>
+  <si>
+    <t>Maharaja Yashwant Rao Holkar Chhatri, Bhanpura</t>
+  </si>
+  <si>
+    <t>24.545000, 75.750000</t>
+  </si>
+  <si>
+    <t>Bade Mahadev, Bhanpura</t>
+  </si>
+  <si>
+    <t>24.550000, 75.740000</t>
+  </si>
+  <si>
+    <t>Mini Goa, Gandhi Sagar, Bhanpura</t>
+  </si>
+  <si>
+    <t>24.710000, 75.555000</t>
+  </si>
+  <si>
+    <t>Kakuni Temple Complex, Kakuni</t>
+  </si>
+  <si>
+    <t>25.055000, 76.650000</t>
+  </si>
+  <si>
+    <t>06-Sep,(Sun) - Day 6</t>
+  </si>
+  <si>
+    <t>Sun Temple, Jhalwarpatan</t>
+  </si>
+  <si>
+    <t>24.845000, 76.165000</t>
+  </si>
+  <si>
+    <t>Shantinath Digamber jain Temple, Jhalwarpatan</t>
+  </si>
+  <si>
+    <t>25.000000, 76.000000</t>
+  </si>
+  <si>
+    <t>Government Museum, Jhalwar</t>
+  </si>
+  <si>
+    <t>24.596000, 76.164000</t>
+  </si>
+  <si>
+    <t>Gagron Fort, Gagron</t>
+  </si>
+  <si>
+    <t>24.602000, 76.165000</t>
+  </si>
+  <si>
+    <t>Gagron Fort View Point, Gagron</t>
+  </si>
+  <si>
+    <t>24.605000, 76.168000</t>
+  </si>
+  <si>
+    <t>Gadiya Mandir, Artu</t>
+  </si>
+  <si>
+    <t>24.500000, 76.200000</t>
+  </si>
+  <si>
+    <t>Temple Ruin, Artu</t>
+  </si>
+  <si>
+    <t>07-Sep,(Mon) - Day 7</t>
+  </si>
+  <si>
+    <t>Sherghare Fort, Shergarh</t>
+  </si>
+  <si>
+    <t>25.100000, 76.700000</t>
+  </si>
+  <si>
+    <t>Kanya Dah Temple Ruin, Baran</t>
+  </si>
+  <si>
+    <t>25.100000, 76.500000</t>
+  </si>
+  <si>
+    <t>Mini Khajuraho Temple, Bansthuni</t>
+  </si>
+  <si>
+    <t>25.100000, 76.400000</t>
+  </si>
+  <si>
+    <t>08-Sep,(Tue) - Day 8</t>
+  </si>
+  <si>
+    <t>Bhand Devara Temple, Ramgarh</t>
+  </si>
+  <si>
+    <t>24.900000, 76.600000</t>
+  </si>
+  <si>
+    <t>Ramghar Mata Temple, Ramgarh</t>
+  </si>
+  <si>
+    <t>Ramghar Creater View, Ramgarh</t>
+  </si>
+  <si>
+    <t>Ramghar Fort, Ramgarh</t>
+  </si>
+  <si>
+    <t>Chauth Mata Mandir, Bundi</t>
+  </si>
+  <si>
+    <t>25.430000, 75.650000</t>
+  </si>
+  <si>
+    <t>RockPainting, Bhimlat</t>
+  </si>
+  <si>
+    <t>25.300000, 75.650000</t>
+  </si>
+  <si>
+    <t>Bhimlat Waterfalls, Bhimlat</t>
+  </si>
+  <si>
+    <t>09-Sep,(Wed) - Day 9</t>
+  </si>
+  <si>
+    <t>Tribal Village, Bhimlat</t>
+  </si>
+  <si>
+    <t>Nagar Sagar Kund, Bundi</t>
+  </si>
+  <si>
+    <t>25.430000, 75.645000</t>
+  </si>
+  <si>
+    <t>Raniji ki Baori, Bundi</t>
+  </si>
+  <si>
+    <t>84 Pillared Cenotaph, Bundi</t>
+  </si>
+  <si>
+    <t>25.422000, 75.650000</t>
+  </si>
+  <si>
+    <t>Sukh Mahal, Bundi</t>
+  </si>
+  <si>
+    <t>25.445000, 75.640000</t>
+  </si>
+  <si>
+    <t>Taragarh Fort, Bundi</t>
+  </si>
+  <si>
+    <t>25.435000, 75.635000</t>
+  </si>
+  <si>
+    <t>7 Wonder Park, Kota</t>
+  </si>
+  <si>
+    <t>25.171000, 75.847000</t>
   </si>
 </sst>
 </file>
@@ -373,7 +623,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\-mmm\ \(ddd\)"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -521,8 +771,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF202020"/>
+      <name val="Aptos"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -708,8 +969,53 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24476B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEADCF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFE2F3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -824,6 +1130,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -869,7 +1184,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -885,6 +1200,57 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="42" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="42" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2411,4 +2777,711 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4100F165-FC32-4953-953B-8807B4A26F03}">
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="65" x14ac:dyDescent="0.35">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="78" x14ac:dyDescent="0.35">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A9" s="11">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="65" x14ac:dyDescent="0.35">
+      <c r="A10" s="11">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A11" s="11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="65" x14ac:dyDescent="0.35">
+      <c r="A12" s="11">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="78" x14ac:dyDescent="0.35">
+      <c r="A13" s="11">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="78" x14ac:dyDescent="0.35">
+      <c r="A14" s="13">
+        <v>13</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A15" s="13">
+        <v>14</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A16" s="13">
+        <v>15</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A17" s="13">
+        <v>16</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A18" s="15">
+        <v>17</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="91" x14ac:dyDescent="0.35">
+      <c r="A19" s="15">
+        <v>18</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A20" s="15">
+        <v>19</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A21" s="15">
+        <v>20</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A22" s="15">
+        <v>21</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A23" s="15">
+        <v>22</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A24" s="15">
+        <v>23</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A25" s="17">
+        <v>24</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="65" x14ac:dyDescent="0.35">
+      <c r="A26" s="17">
+        <v>25</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="65" x14ac:dyDescent="0.35">
+      <c r="A27" s="17">
+        <v>26</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A28" s="19">
+        <v>27</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A29" s="19">
+        <v>28</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A30" s="19">
+        <v>29</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A31" s="19">
+        <v>30</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A32" s="19">
+        <v>31</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A33" s="19">
+        <v>32</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A34" s="19">
+        <v>33</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A35" s="21">
+        <v>34</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A36" s="21">
+        <v>35</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A37" s="21">
+        <v>36</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A38" s="21">
+        <v>37</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C38" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A39" s="21">
+        <v>38</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A40" s="21">
+        <v>39</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+      <c r="A41" s="21">
+        <v>40</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/travelsheet.xlsx
+++ b/travelsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\@master_repo\workstation\social-post\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E114A655-6EBA-4435-9FCF-2704ACE85D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B947FDAB-5FD6-4E14-8B3A-55AD3B17C496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1202,55 +1202,55 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="38" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="38" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="39" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="39" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="40" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="40" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="41" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="41" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="42" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="42" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2783,6 +2783,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4100F165-FC32-4953-953B-8807B4A26F03}">
   <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.7265625" style="3"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
@@ -2801,7 +2809,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -2818,7 +2826,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -2835,7 +2843,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -2852,7 +2860,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -2869,7 +2877,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -2886,7 +2894,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="65" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -2903,7 +2911,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="78" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -2920,7 +2928,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <v>8</v>
       </c>
@@ -2937,7 +2945,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="65" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <v>9</v>
       </c>
@@ -2954,7 +2962,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <v>10</v>
       </c>
@@ -2971,7 +2979,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="65" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <v>11</v>
       </c>
@@ -2988,7 +2996,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="78" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <v>12</v>
       </c>
@@ -3005,7 +3013,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="78" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="13">
         <v>13</v>
       </c>
@@ -3022,7 +3030,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="13">
         <v>14</v>
       </c>
@@ -3039,7 +3047,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="13">
         <v>15</v>
       </c>
@@ -3056,7 +3064,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="13">
         <v>16</v>
       </c>
@@ -3073,7 +3081,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="15">
         <v>17</v>
       </c>
@@ -3090,7 +3098,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="91" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="15">
         <v>18</v>
       </c>
@@ -3107,7 +3115,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="15">
         <v>19</v>
       </c>
@@ -3124,7 +3132,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="15">
         <v>20</v>
       </c>
@@ -3141,7 +3149,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="15">
         <v>21</v>
       </c>
@@ -3158,7 +3166,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="15">
         <v>22</v>
       </c>
@@ -3175,7 +3183,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="15">
         <v>23</v>
       </c>
@@ -3192,7 +3200,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="17">
         <v>24</v>
       </c>
@@ -3209,7 +3217,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="65" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="17">
         <v>25</v>
       </c>
@@ -3226,7 +3234,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="65" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="17">
         <v>26</v>
       </c>
@@ -3243,7 +3251,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="19">
         <v>27</v>
       </c>
@@ -3260,7 +3268,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="19">
         <v>28</v>
       </c>
@@ -3277,7 +3285,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="19">
         <v>29</v>
       </c>
@@ -3294,7 +3302,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="19">
         <v>30</v>
       </c>
@@ -3311,7 +3319,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="19">
         <v>31</v>
       </c>
@@ -3328,7 +3336,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="19">
         <v>32</v>
       </c>
@@ -3345,7 +3353,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="19">
         <v>33</v>
       </c>
@@ -3362,7 +3370,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="21">
         <v>34</v>
       </c>
@@ -3379,7 +3387,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="21">
         <v>35</v>
       </c>
@@ -3396,7 +3404,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="21">
         <v>36</v>
       </c>
@@ -3413,7 +3421,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="21">
         <v>37</v>
       </c>
@@ -3430,7 +3438,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="21">
         <v>38</v>
       </c>
@@ -3447,7 +3455,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="21">
         <v>39</v>
       </c>
@@ -3464,7 +3472,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="52" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="21">
         <v>40</v>
       </c>
